--- a/data/trans_orig/PCS12_SP-Clase-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media del componente de salud física (SF12)</t>
+          <t>Puntuación media del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,27; 53,85</t>
+          <t>52,36; 53,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,17; 54,39</t>
+          <t>53,27; 54,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,77; 54,16</t>
+          <t>52,78; 54,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,24; 53,51</t>
+          <t>52,33; 53,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,86; 52,87</t>
+          <t>50,97; 52,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,96; 53,65</t>
+          <t>51,93; 53,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,96; 53,86</t>
+          <t>51,91; 53,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,46; 52,73</t>
+          <t>51,5; 52,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,14; 53,33</t>
+          <t>52,12; 53,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52,92; 53,91</t>
+          <t>52,94; 53,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,68; 53,8</t>
+          <t>52,68; 53,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,1; 53,0</t>
+          <t>52,06; 52,93</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,27; 54,53</t>
+          <t>53,3; 54,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,0; 53,6</t>
+          <t>51,98; 53,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,99; 54,49</t>
+          <t>53,03; 54,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,65; 52,96</t>
+          <t>51,63; 52,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,69; 54,07</t>
+          <t>52,71; 54,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,13; 53,77</t>
+          <t>52,17; 53,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,97; 53,84</t>
+          <t>52,09; 53,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,06; 52,56</t>
+          <t>50,92; 52,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,18; 54,15</t>
+          <t>53,2; 54,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52,37; 53,52</t>
+          <t>52,35; 53,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,86; 54,05</t>
+          <t>52,86; 53,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,61; 52,6</t>
+          <t>51,6; 52,6</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,23; 53,45</t>
+          <t>52,29; 53,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,52; 52,15</t>
+          <t>50,53; 52,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,93; 53,17</t>
+          <t>51,87; 53,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,94; 50,9</t>
+          <t>49,0; 51,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,92; 51,24</t>
+          <t>47,88; 51,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,68; 51,19</t>
+          <t>48,72; 51,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,17; 51,48</t>
+          <t>47,99; 51,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,29; 49,06</t>
+          <t>46,25; 49,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,54; 52,69</t>
+          <t>51,48; 52,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50,24; 51,59</t>
+          <t>50,29; 51,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,15; 52,52</t>
+          <t>51,22; 52,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,75; 50,25</t>
+          <t>48,7; 50,21</t>
         </is>
       </c>
     </row>
@@ -1136,42 +1136,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,53; 52,4</t>
+          <t>51,5; 52,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,86; 52,0</t>
+          <t>50,9; 52,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,49; 52,49</t>
+          <t>51,46; 52,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,66; 50,97</t>
+          <t>49,68; 50,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,62; 51,93</t>
+          <t>50,57; 51,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,95; 52,25</t>
+          <t>50,95; 52,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,22; 52,48</t>
+          <t>51,25; 52,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,35; 52,13</t>
+          <t>50,35; 52,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51,12; 51,99</t>
+          <t>51,11; 51,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,58; 52,38</t>
+          <t>51,56; 52,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,24; 51,51</t>
+          <t>50,25; 51,48</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>50,9; 52,63</t>
+          <t>50,94; 52,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,94; 52,49</t>
+          <t>50,9; 52,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,57; 52,04</t>
+          <t>50,57; 52,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,64; 50,6</t>
+          <t>48,81; 50,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,62; 51,14</t>
+          <t>49,64; 51,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,84; 48,54</t>
+          <t>46,82; 48,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,07; 49,71</t>
+          <t>48,14; 49,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,12; 50,26</t>
+          <t>46,94; 49,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,48; 51,65</t>
+          <t>50,34; 51,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,72; 49,94</t>
+          <t>48,73; 49,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49,44; 50,61</t>
+          <t>49,46; 50,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,96; 49,91</t>
+          <t>48,02; 49,94</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54,68; 55,74</t>
+          <t>54,65; 55,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54,18; 55,59</t>
+          <t>54,12; 55,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,19; 56,19</t>
+          <t>55,14; 56,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55,13; 56,23</t>
+          <t>55,11; 56,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,96; 49,12</t>
+          <t>47,97; 49,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,18; 48,65</t>
+          <t>47,16; 48,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,79; 49,25</t>
+          <t>47,84; 49,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,11; 48,58</t>
+          <t>47,09; 48,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49,33; 50,38</t>
+          <t>49,34; 50,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48,63; 49,91</t>
+          <t>48,67; 49,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49,42; 50,67</t>
+          <t>49,48; 50,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>49,06; 50,35</t>
+          <t>49,09; 50,35</t>
         </is>
       </c>
     </row>
@@ -1556,52 +1556,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>52,51; 53,03</t>
+          <t>52,54; 53,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51,93; 52,55</t>
+          <t>51,92; 52,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52,4; 52,96</t>
+          <t>52,43; 52,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,6; 51,58</t>
+          <t>50,64; 51,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,02; 50,65</t>
+          <t>50,04; 50,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,39; 50,11</t>
+          <t>49,4; 50,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,05; 50,76</t>
+          <t>50,04; 50,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>49,34; 50,41</t>
+          <t>49,31; 50,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,37; 51,79</t>
+          <t>51,35; 51,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50,75; 51,22</t>
+          <t>50,77; 51,22</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,18; 50,81</t>
+          <t>50,17; 50,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/PCS12_SP-Clase-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52,93</t>
+          <t>52,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,12</t>
+          <t>52,04</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,55</t>
+          <t>52,51</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,36; 53,82</t>
+          <t>52,38; 53,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,27; 54,43</t>
+          <t>53,23; 54,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,78; 54,17</t>
+          <t>52,72; 54,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,33; 53,5</t>
+          <t>52,32; 53,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,97; 52,86</t>
+          <t>50,92; 52,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,93; 53,67</t>
+          <t>51,91; 53,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,91; 53,76</t>
+          <t>52,0; 53,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,5; 52,67</t>
+          <t>51,39; 52,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,12; 53,33</t>
+          <t>52,11; 53,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52,94; 53,92</t>
+          <t>52,94; 53,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,68; 53,83</t>
+          <t>52,63; 53,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,06; 52,93</t>
+          <t>52,06; 52,95</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52,39</t>
+          <t>52,49</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51,75</t>
+          <t>51,69</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52,1</t>
+          <t>52,12</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,3; 54,52</t>
+          <t>53,36; 54,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,98; 53,6</t>
+          <t>51,99; 53,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,03; 54,43</t>
+          <t>53,06; 54,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,63; 52,97</t>
+          <t>51,76; 53,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,71; 54,09</t>
+          <t>52,71; 54,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,17; 53,86</t>
+          <t>52,19; 53,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,09; 53,82</t>
+          <t>52,03; 53,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,92; 52,44</t>
+          <t>50,91; 52,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,2; 54,17</t>
+          <t>53,22; 54,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52,35; 53,51</t>
+          <t>52,27; 53,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,86; 53,97</t>
+          <t>52,86; 53,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,6; 52,6</t>
+          <t>51,64; 52,55</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49,92</t>
+          <t>50,94</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,78</t>
+          <t>47,94</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,49</t>
+          <t>50,08</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,29; 53,46</t>
+          <t>52,24; 53,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,53; 52,12</t>
+          <t>50,34; 52,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,87; 53,21</t>
+          <t>51,82; 53,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,0; 51,02</t>
+          <t>50,11; 51,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,88; 51,16</t>
+          <t>47,93; 51,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,72; 51,17</t>
+          <t>48,96; 51,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,99; 51,4</t>
+          <t>47,99; 51,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,25; 49,06</t>
+          <t>46,41; 49,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,48; 52,7</t>
+          <t>51,48; 52,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50,29; 51,58</t>
+          <t>50,24; 51,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,22; 52,5</t>
+          <t>51,17; 52,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,7; 50,21</t>
+          <t>49,34; 50,73</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50,34</t>
+          <t>50,39</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,11</t>
+          <t>50,56</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,72</t>
+          <t>50,46</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,5; 52,36</t>
+          <t>51,48; 52,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,9; 52,07</t>
+          <t>50,91; 52,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,46; 52,56</t>
+          <t>51,5; 52,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,68; 50,91</t>
+          <t>49,8; 50,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,57; 51,91</t>
+          <t>50,64; 51,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,95; 52,28</t>
+          <t>50,95; 52,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,25; 52,56</t>
+          <t>51,17; 52,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,35; 52,17</t>
+          <t>50,06; 51,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,35; 52,07</t>
+          <t>51,34; 52,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51,11; 51,96</t>
+          <t>51,08; 51,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,56; 52,39</t>
+          <t>51,55; 52,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,25; 51,48</t>
+          <t>50,05; 50,84</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49,76</t>
+          <t>50,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48,12</t>
+          <t>47,35</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48,71</t>
+          <t>48,54</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>50,94; 52,62</t>
+          <t>50,82; 52,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,9; 52,46</t>
+          <t>50,91; 52,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,57; 52,03</t>
+          <t>50,43; 51,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,81; 50,67</t>
+          <t>49,34; 50,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,64; 51,11</t>
+          <t>49,52; 51,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,82; 48,55</t>
+          <t>46,83; 48,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,14; 49,83</t>
+          <t>48,15; 49,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,94; 49,96</t>
+          <t>46,75; 48,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,34; 51,51</t>
+          <t>50,35; 51,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,73; 49,91</t>
+          <t>48,74; 49,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49,46; 50,61</t>
+          <t>49,46; 50,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,02; 49,94</t>
+          <t>48,02; 49,03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55,69</t>
+          <t>55,66</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47,84</t>
+          <t>48,0</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,74</t>
+          <t>49,7</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54,65; 55,74</t>
+          <t>54,75; 55,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54,12; 55,56</t>
+          <t>54,24; 55,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,14; 56,19</t>
+          <t>55,21; 56,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55,11; 56,27</t>
+          <t>55,04; 56,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,97; 49,06</t>
+          <t>47,97; 49,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,16; 48,59</t>
+          <t>47,1; 48,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,84; 49,37</t>
+          <t>47,83; 49,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,09; 48,48</t>
+          <t>47,24; 48,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49,34; 50,32</t>
+          <t>49,38; 50,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48,67; 49,88</t>
+          <t>48,71; 49,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49,48; 50,63</t>
+          <t>49,42; 50,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>49,09; 50,35</t>
+          <t>49,09; 50,3</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51,22</t>
+          <t>51,52</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>49,75</t>
+          <t>49,43</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,47</t>
+          <t>50,45</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>52,54; 53,04</t>
+          <t>52,53; 53,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51,92; 52,56</t>
+          <t>51,95; 52,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52,43; 52,99</t>
+          <t>52,41; 52,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,64; 51,57</t>
+          <t>51,22; 51,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,04; 50,69</t>
+          <t>50,01; 50,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,4; 50,11</t>
+          <t>49,43; 50,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,04; 50,75</t>
+          <t>50,04; 50,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>49,31; 50,37</t>
+          <t>49,13; 49,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,35; 51,76</t>
+          <t>51,37; 51,79</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50,77; 51,22</t>
+          <t>50,75; 51,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51,29; 51,76</t>
+          <t>51,27; 51,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,17; 50,79</t>
+          <t>50,24; 50,64</t>
         </is>
       </c>
     </row>
